--- a/output/validation.xlsx
+++ b/output/validation.xlsx
@@ -485,23 +485,27 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>-4</v>
+        <v>-16</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>13.57</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>0.065</v>
+        <v>0.352</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -532,10 +536,10 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="J3" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="4">
@@ -570,10 +574,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.16</v>
+        <v>0.238</v>
       </c>
       <c r="J4" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="5">
@@ -604,10 +608,10 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="J5" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="6">
@@ -638,10 +642,10 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.034</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="7">
@@ -672,10 +676,10 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.04</v>
+        <v>0.067</v>
       </c>
       <c r="J7" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="8">
@@ -693,10 +697,10 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
@@ -706,82 +710,82 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.156</v>
+        <v>0.186</v>
       </c>
       <c r="J8" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>13.16</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>0.098</v>
+        <v>0.101</v>
       </c>
       <c r="J9" t="n">
-        <v>2.59</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G10" t="n">
-        <v>13.16</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>16.18</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>0.111</v>
       </c>
       <c r="J10" t="n">
-        <v>5.29</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="11">
@@ -799,10 +803,10 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -812,10 +816,10 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.05</v>
+        <v>0.053</v>
       </c>
       <c r="J11" t="n">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="12">
@@ -846,10 +850,10 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.206</v>
+        <v>0.221</v>
       </c>
       <c r="J12" t="n">
-        <v>3.46</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="13">
@@ -880,89 +884,89 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.207</v>
+        <v>0.272</v>
       </c>
       <c r="J13" t="n">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>James Cook</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>13.98</v>
+        <v>15.68</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.19</v>
+        <v>0.042</v>
       </c>
       <c r="J14" t="n">
-        <v>3.57</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>James Cook</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>15.68</v>
+        <v>13.98</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.04</v>
+        <v>0.224</v>
       </c>
       <c r="J15" t="n">
-        <v>7.04</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brock Bowers</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -975,85 +979,85 @@
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>14.54</v>
+        <v>15.68</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.081</v>
+        <v>0.047</v>
       </c>
       <c r="J16" t="n">
-        <v>4.94</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>-19</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>15.68</v>
+        <v>13.03</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.04</v>
+        <v>0.374</v>
       </c>
       <c r="J17" t="n">
-        <v>5.79</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Brock Bowers</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
-        <v>13.03</v>
+        <v>14.54</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.306</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>6.12</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="19">
@@ -1071,10 +1075,10 @@
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F19" t="n">
         <v>19</v>
@@ -1084,112 +1088,112 @@
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.163</v>
+        <v>0.177</v>
       </c>
       <c r="J19" t="n">
-        <v>5.94</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>De'Von Achane</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>15.68</v>
+        <v>15.8</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.033</v>
+        <v>0.058</v>
       </c>
       <c r="J20" t="n">
-        <v>6.87</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>20</v>
       </c>
       <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="n">
         <v>11</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>9</v>
       </c>
-      <c r="F21" t="n">
-        <v>21</v>
-      </c>
       <c r="G21" t="n">
-        <v>15.8</v>
+        <v>15.68</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.041</v>
+        <v>0.05</v>
       </c>
       <c r="J21" t="n">
-        <v>4.36</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>-42</v>
+        <v>-12</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
-        <v>11.67</v>
+        <v>14.33</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.41</v>
+        <v>0.145</v>
       </c>
       <c r="J22" t="n">
-        <v>8.779999999999999</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="23">
@@ -1207,10 +1211,10 @@
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="F23" t="n">
         <v>27</v>
@@ -1220,71 +1224,75 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.23</v>
+        <v>0.232</v>
       </c>
       <c r="J23" t="n">
-        <v>7.08</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>171</v>
       </c>
       <c r="E24" t="n">
-        <v>-14</v>
+        <v>-148</v>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="G24" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>10.09</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.124</v>
+        <v>0.836</v>
       </c>
       <c r="J24" t="n">
-        <v>6.56</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Kenneth Walker</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>184</v>
+        <v>53</v>
       </c>
       <c r="E25" t="n">
-        <v>-160</v>
+        <v>-29</v>
       </c>
       <c r="F25" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
-        <v>10.09</v>
+        <v>12.1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1292,112 +1300,112 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.855</v>
+        <v>0.318</v>
       </c>
       <c r="J25" t="n">
-        <v>9.23</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E26" t="n">
-        <v>-14</v>
+        <v>-35</v>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="G26" t="n">
-        <v>11.85</v>
+        <v>11.67</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.222</v>
+        <v>0.469</v>
       </c>
       <c r="J26" t="n">
-        <v>7.4</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Josh Allen</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>16.37</v>
+        <v>11.85</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.266</v>
       </c>
       <c r="J27" t="n">
-        <v>2.58</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kenneth Walker</t>
+          <t>Josh Allen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F28" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G28" t="n">
-        <v>14.1</v>
+        <v>16.37</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.118</v>
+        <v>0.1</v>
       </c>
       <c r="J28" t="n">
-        <v>9.68</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="29">
@@ -1415,10 +1423,10 @@
         <v>28</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E29" t="n">
-        <v>-32</v>
+        <v>-30</v>
       </c>
       <c r="F29" t="n">
         <v>57</v>
@@ -1432,10 +1440,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.21</v>
+        <v>0.288</v>
       </c>
       <c r="J29" t="n">
-        <v>13.65</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="30">
@@ -1453,10 +1461,10 @@
         <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E30" t="n">
-        <v>-57</v>
+        <v>-50</v>
       </c>
       <c r="F30" t="n">
         <v>45</v>
@@ -1466,10 +1474,10 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.476</v>
+        <v>0.532</v>
       </c>
       <c r="J30" t="n">
-        <v>7.61</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="31">
@@ -1487,23 +1495,27 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
         <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>15.38</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.144</v>
+        <v>0.214</v>
       </c>
       <c r="J31" t="n">
-        <v>7.85</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1521,10 +1533,10 @@
         <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="E32" t="n">
-        <v>-11</v>
+        <v>-38</v>
       </c>
       <c r="F32" t="n">
         <v>48</v>
@@ -1534,16 +1546,16 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.214</v>
+        <v>0.316</v>
       </c>
       <c r="J32" t="n">
-        <v>9.51</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1555,23 +1567,23 @@
         <v>32</v>
       </c>
       <c r="D33" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G33" t="n">
-        <v>15.81</v>
+        <v>15.24</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.22</v>
+        <v>0.234</v>
       </c>
       <c r="J33" t="n">
-        <v>6.7</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="34">
@@ -1589,10 +1601,10 @@
         <v>33</v>
       </c>
       <c r="D34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E34" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="F34" t="n">
         <v>49</v>
@@ -1602,16 +1614,16 @@
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.286</v>
+        <v>0.295</v>
       </c>
       <c r="J34" t="n">
-        <v>7.19</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1623,159 +1635,159 @@
         <v>34</v>
       </c>
       <c r="D35" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>15.24</v>
+        <v>15.81</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.212</v>
+        <v>0.241</v>
       </c>
       <c r="J35" t="n">
-        <v>7.51</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>35</v>
       </c>
       <c r="D36" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G36" t="n">
-        <v>13.98</v>
+        <v>15.25</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.259</v>
+        <v>0.098</v>
       </c>
       <c r="J36" t="n">
-        <v>6.74</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>36</v>
       </c>
       <c r="D37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F37" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G37" t="n">
-        <v>13.29</v>
+        <v>13.98</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.15</v>
+        <v>0.258</v>
       </c>
       <c r="J37" t="n">
-        <v>8.699999999999999</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>37</v>
       </c>
       <c r="D38" t="n">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="E38" t="n">
-        <v>-40</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G38" t="n">
-        <v>15.11</v>
+        <v>13.29</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.29</v>
+        <v>0.152</v>
       </c>
       <c r="J38" t="n">
-        <v>14.4</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Drake Maye</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>38</v>
       </c>
       <c r="D39" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="E39" t="n">
-        <v>23</v>
+        <v>-42</v>
       </c>
       <c r="F39" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G39" t="n">
-        <v>15.25</v>
+        <v>15.11</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.076</v>
+        <v>0.293</v>
       </c>
       <c r="J39" t="n">
-        <v>13.56</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="40">
@@ -1793,10 +1805,10 @@
         <v>39</v>
       </c>
       <c r="D40" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
         <v>38</v>
@@ -1810,10 +1822,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.123</v>
+        <v>0.116</v>
       </c>
       <c r="J40" t="n">
-        <v>6.75</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="41">
@@ -1831,10 +1843,10 @@
         <v>40</v>
       </c>
       <c r="D41" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E41" t="n">
-        <v>-55</v>
+        <v>-52</v>
       </c>
       <c r="F41" t="n">
         <v>77</v>
@@ -1848,16 +1860,16 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.484</v>
+        <v>0.513</v>
       </c>
       <c r="J41" t="n">
-        <v>7.62</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1869,33 +1881,29 @@
         <v>41</v>
       </c>
       <c r="D42" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F42" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G42" t="n">
-        <v>12.68</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>15.68</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.308</v>
+        <v>0.078</v>
       </c>
       <c r="J42" t="n">
-        <v>8.24</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1907,29 +1915,33 @@
         <v>42</v>
       </c>
       <c r="D43" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E43" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G43" t="n">
-        <v>15.68</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>12.68</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.063</v>
+        <v>0.319</v>
       </c>
       <c r="J43" t="n">
-        <v>7.09</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1941,135 +1953,135 @@
         <v>43</v>
       </c>
       <c r="D44" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="E44" t="n">
-        <v>-8</v>
+        <v>20</v>
       </c>
       <c r="F44" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G44" t="n">
-        <v>13.24</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>15.68</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.209</v>
+        <v>0.081</v>
       </c>
       <c r="J44" t="n">
-        <v>7.26</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>44</v>
       </c>
       <c r="D45" t="n">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="E45" t="n">
-        <v>21</v>
+        <v>-120</v>
       </c>
       <c r="F45" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="G45" t="n">
-        <v>15.68</v>
+        <v>13.54</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.068</v>
+        <v>0.575</v>
       </c>
       <c r="J45" t="n">
-        <v>6.19</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Travis Etienne</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E46" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G46" t="n">
-        <v>13.73</v>
+        <v>15.36</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.37</v>
+        <v>0.123</v>
       </c>
       <c r="J46" t="n">
-        <v>6.23</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Luther Burden</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>46</v>
       </c>
       <c r="D47" t="n">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="E47" t="n">
-        <v>-55</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G47" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>14.09</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.385</v>
+        <v>0.327</v>
       </c>
       <c r="J47" t="n">
-        <v>14.24</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Luther Burden</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2081,33 +2093,29 @@
         <v>47</v>
       </c>
       <c r="D48" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="F48" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="G48" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>13.73</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.304</v>
+        <v>0.388</v>
       </c>
       <c r="J48" t="n">
-        <v>8.84</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Travis Etienne</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2119,23 +2127,27 @@
         <v>48</v>
       </c>
       <c r="D49" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="F49" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G49" t="n">
-        <v>15.36</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>13.24</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.12</v>
+        <v>0.236</v>
       </c>
       <c r="J49" t="n">
-        <v>7.22</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="50">
@@ -2153,10 +2165,10 @@
         <v>49</v>
       </c>
       <c r="D50" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E50" t="n">
-        <v>-55</v>
+        <v>-51</v>
       </c>
       <c r="F50" t="n">
         <v>62</v>
@@ -2166,10 +2178,10 @@
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>0.512</v>
+        <v>0.537</v>
       </c>
       <c r="J50" t="n">
-        <v>7.78</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="51">
@@ -2187,10 +2199,10 @@
         <v>50</v>
       </c>
       <c r="D51" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E51" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="F51" t="n">
         <v>65</v>
@@ -2200,120 +2212,116 @@
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>0.356</v>
+        <v>0.368</v>
       </c>
       <c r="J51" t="n">
-        <v>13.51</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Tyler Warren</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>51</v>
       </c>
       <c r="D52" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="E52" t="n">
-        <v>-39</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G52" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>14.11</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.358</v>
+        <v>0.21</v>
       </c>
       <c r="J52" t="n">
-        <v>16.59</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tyler Warren</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>52</v>
       </c>
       <c r="D53" t="n">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>-67</v>
       </c>
       <c r="F53" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G53" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>13.22</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
-        <v>11.09</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>53</v>
       </c>
       <c r="D54" t="n">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="E54" t="n">
-        <v>-114</v>
+        <v>8</v>
       </c>
       <c r="F54" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G54" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>15.68</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>0.783</v>
+        <v>0.104</v>
       </c>
       <c r="J54" t="n">
-        <v>10.27</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="55">
@@ -2331,10 +2339,10 @@
         <v>54</v>
       </c>
       <c r="D55" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F55" t="n">
         <v>35</v>
@@ -2344,78 +2352,82 @@
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>0.244</v>
+        <v>0.27</v>
       </c>
       <c r="J55" t="n">
-        <v>10.24</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>55</v>
       </c>
       <c r="D56" t="n">
-        <v>44</v>
+        <v>163</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>-108</v>
       </c>
       <c r="F56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G56" t="n">
-        <v>15.68</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>9.51</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.1</v>
+        <v>0.772</v>
       </c>
       <c r="J56" t="n">
-        <v>7.96</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>56</v>
       </c>
       <c r="D57" t="n">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="E57" t="n">
-        <v>-20</v>
+        <v>26</v>
       </c>
       <c r="F57" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G57" t="n">
-        <v>11.39</v>
+        <v>15.43</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>0.303</v>
+        <v>0.157</v>
       </c>
       <c r="J57" t="n">
-        <v>8.68</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="58">
@@ -2433,10 +2445,10 @@
         <v>57</v>
       </c>
       <c r="D58" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E58" t="n">
-        <v>-48</v>
+        <v>-42</v>
       </c>
       <c r="F58" t="n">
         <v>80</v>
@@ -2446,50 +2458,50 @@
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>0.522</v>
+        <v>0.521</v>
       </c>
       <c r="J58" t="n">
-        <v>8.73</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>58</v>
       </c>
       <c r="D59" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E59" t="n">
-        <v>9</v>
+        <v>-5</v>
       </c>
       <c r="F59" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="G59" t="n">
-        <v>15.43</v>
+        <v>13.35</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>0.222</v>
+        <v>0.435</v>
       </c>
       <c r="J59" t="n">
-        <v>11.41</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2501,57 +2513,57 @@
         <v>59</v>
       </c>
       <c r="D60" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>-10</v>
+        <v>-18</v>
       </c>
       <c r="F60" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="G60" t="n">
-        <v>13.79</v>
+        <v>11.39</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>0.22</v>
+        <v>0.342</v>
       </c>
       <c r="J60" t="n">
-        <v>8.68</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>60</v>
       </c>
       <c r="D61" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="F61" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="G61" t="n">
-        <v>13.35</v>
+        <v>13.79</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>0.414</v>
+        <v>0.242</v>
       </c>
       <c r="J61" t="n">
-        <v>10.68</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="62">
@@ -2569,10 +2581,10 @@
         <v>61</v>
       </c>
       <c r="D62" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E62" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F62" t="n">
         <v>30</v>
@@ -2582,10 +2594,10 @@
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>0.119</v>
+        <v>0.131</v>
       </c>
       <c r="J62" t="n">
-        <v>8.529999999999999</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="63">
@@ -2603,27 +2615,23 @@
         <v>62</v>
       </c>
       <c r="D63" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E63" t="n">
-        <v>-13</v>
+        <v>5</v>
       </c>
       <c r="F63" t="n">
         <v>76</v>
       </c>
       <c r="G63" t="n">
-        <v>13.81</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>14.61</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>0.229</v>
+        <v>0.172</v>
       </c>
       <c r="J63" t="n">
-        <v>8.890000000000001</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="64">
@@ -2641,235 +2649,231 @@
         <v>63</v>
       </c>
       <c r="D64" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E64" t="n">
-        <v>-8</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>83</v>
       </c>
       <c r="G64" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>15.87</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>0.39</v>
+        <v>0.357</v>
       </c>
       <c r="J64" t="n">
-        <v>16.35</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>64</v>
       </c>
       <c r="D65" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="E65" t="n">
-        <v>-10</v>
+        <v>46</v>
       </c>
       <c r="F65" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G65" t="n">
-        <v>14.79</v>
+        <v>16.37</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>0.52</v>
+        <v>0.154</v>
       </c>
       <c r="J65" t="n">
-        <v>14.93</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>65</v>
       </c>
       <c r="D66" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="E66" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="G66" t="n">
-        <v>16.37</v>
+        <v>14.61</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>0.116</v>
+        <v>0.205</v>
       </c>
       <c r="J66" t="n">
-        <v>14.22</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>66</v>
       </c>
       <c r="D67" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="F67" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="G67" t="n">
-        <v>14.61</v>
+        <v>14.79</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>0.196</v>
+        <v>0.518</v>
       </c>
       <c r="J67" t="n">
-        <v>10.44</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Marvin Harrison</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>67</v>
       </c>
       <c r="D68" t="n">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="E68" t="n">
-        <v>15</v>
+        <v>-57</v>
       </c>
       <c r="F68" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="G68" t="n">
-        <v>14.73</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>14.61</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>0.156</v>
+        <v>0.578</v>
       </c>
       <c r="J68" t="n">
-        <v>10.13</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Marvin Harrison</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>68</v>
       </c>
       <c r="D69" t="n">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="E69" t="n">
-        <v>-61</v>
+        <v>20</v>
       </c>
       <c r="F69" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G69" t="n">
-        <v>14.61</v>
+        <v>16.06</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>0.546</v>
+        <v>0.172</v>
       </c>
       <c r="J69" t="n">
-        <v>11.64</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>69</v>
       </c>
       <c r="D70" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="G70" t="n">
-        <v>16.06</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>14.73</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.249</v>
+        <v>0.176</v>
       </c>
       <c r="J70" t="n">
-        <v>13.49</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -2887,10 +2891,10 @@
         <v>70</v>
       </c>
       <c r="D71" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E71" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
         <v>131</v>
@@ -2900,10 +2904,10 @@
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>0.327</v>
+        <v>0.339</v>
       </c>
       <c r="J71" t="n">
-        <v>8.9</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="72">
@@ -2921,10 +2925,10 @@
         <v>71</v>
       </c>
       <c r="D72" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E72" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F72" t="n">
         <v>61</v>
@@ -2934,54 +2938,50 @@
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>0.18</v>
+        <v>0.194</v>
       </c>
       <c r="J72" t="n">
-        <v>12.33</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Chris Godwin</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E73" t="n">
-        <v>-111</v>
+        <v>-96</v>
       </c>
       <c r="F73" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="G73" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>10.33</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="J73" t="n">
-        <v>13.96</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2993,258 +2993,262 @@
         <v>73</v>
       </c>
       <c r="D74" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="E74" t="n">
-        <v>37</v>
+        <v>-17</v>
       </c>
       <c r="F74" t="n">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="G74" t="n">
-        <v>15.05</v>
+        <v>13.93</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>0.113</v>
+        <v>0.286</v>
       </c>
       <c r="J74" t="n">
-        <v>8.09</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Chris Godwin</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>74</v>
       </c>
       <c r="D75" t="n">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="E75" t="n">
-        <v>-99</v>
+        <v>-53</v>
       </c>
       <c r="F75" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="G75" t="n">
-        <v>10.33</v>
+        <v>13.54</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>0.788</v>
+        <v>0.385</v>
       </c>
       <c r="J75" t="n">
-        <v>13.97</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>75</v>
       </c>
       <c r="D76" t="n">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="E76" t="n">
-        <v>-38</v>
+        <v>37</v>
       </c>
       <c r="F76" t="n">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="G76" t="n">
-        <v>14.17</v>
+        <v>15.05</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>0.384</v>
+        <v>0.124</v>
       </c>
       <c r="J76" t="n">
-        <v>13.74</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Brian Thomas</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>76</v>
       </c>
       <c r="D77" t="n">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="E77" t="n">
-        <v>-33</v>
+        <v>-56</v>
       </c>
       <c r="F77" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G77" t="n">
-        <v>15.24</v>
+        <v>14.17</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>0.49</v>
+        <v>0.383</v>
       </c>
       <c r="J77" t="n">
-        <v>14.91</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Kyle Pitts</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>77</v>
       </c>
       <c r="D78" t="n">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="E78" t="n">
-        <v>-34</v>
+        <v>40</v>
       </c>
       <c r="F78" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G78" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>16.12</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
-        <v>0.515</v>
+        <v>0.172</v>
       </c>
       <c r="J78" t="n">
-        <v>13.1</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>78</v>
       </c>
       <c r="D79" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E79" t="n">
-        <v>-22</v>
+        <v>-32</v>
       </c>
       <c r="F79" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G79" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
+        <v>14.12</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.381</v>
+        <v>0.546</v>
       </c>
       <c r="J79" t="n">
-        <v>13.76</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Brian Thomas</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>79</v>
       </c>
       <c r="D80" t="n">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="E80" t="n">
-        <v>-14</v>
+        <v>-74</v>
       </c>
       <c r="F80" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G80" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
+        <v>13.44</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.27</v>
+        <v>0.701</v>
       </c>
       <c r="J80" t="n">
-        <v>9.140000000000001</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Michael Pittman</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>80</v>
       </c>
       <c r="D81" t="n">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="E81" t="n">
-        <v>-54</v>
+        <v>-100</v>
       </c>
       <c r="F81" t="n">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="G81" t="n">
-        <v>15.07</v>
+        <v>8.49</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3252,44 +3256,48 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>14.1</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kyle Pitts</t>
+          <t>Michael Pittman</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>81</v>
       </c>
       <c r="D82" t="n">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="E82" t="n">
-        <v>43</v>
+        <v>-50</v>
       </c>
       <c r="F82" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G82" t="n">
-        <v>16.12</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>15.07</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.123</v>
+        <v>0.582</v>
       </c>
       <c r="J82" t="n">
-        <v>10.15</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="83">
@@ -3307,10 +3315,10 @@
         <v>82</v>
       </c>
       <c r="D83" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E83" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="F83" t="n">
         <v>100</v>
@@ -3320,10 +3328,10 @@
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>0.48</v>
+        <v>0.473</v>
       </c>
       <c r="J83" t="n">
-        <v>15.08</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="84">
@@ -3341,10 +3349,10 @@
         <v>83</v>
       </c>
       <c r="D84" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E84" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="F84" t="n">
         <v>110</v>
@@ -3354,37 +3362,37 @@
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>0.256</v>
+        <v>0.282</v>
       </c>
       <c r="J84" t="n">
-        <v>10.23</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sam LaPorta</t>
+          <t>Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>84</v>
       </c>
       <c r="D85" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E85" t="n">
-        <v>-32</v>
+        <v>-55</v>
       </c>
       <c r="F85" t="n">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="G85" t="n">
-        <v>11.49</v>
+        <v>15.07</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3392,50 +3400,54 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.457</v>
+        <v>0.622</v>
       </c>
       <c r="J85" t="n">
-        <v>13.85</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson</t>
+          <t>Sam LaPorta</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>85</v>
       </c>
       <c r="D86" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E86" t="n">
-        <v>-41</v>
+        <v>-33</v>
       </c>
       <c r="F86" t="n">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="G86" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>11.49</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.538</v>
+        <v>0.507</v>
       </c>
       <c r="J86" t="n">
-        <v>15.23</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Josh Downs</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3447,29 +3459,33 @@
         <v>86</v>
       </c>
       <c r="D87" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="F87" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="G87" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
+        <v>14.12</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.43</v>
+        <v>0.462</v>
       </c>
       <c r="J87" t="n">
-        <v>16.04</v>
+        <v>14.57</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Josh Downs</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3481,23 +3497,23 @@
         <v>87</v>
       </c>
       <c r="D88" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F88" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="G88" t="n">
-        <v>14.92</v>
+        <v>15.87</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
-        <v>0.361</v>
+        <v>0.434</v>
       </c>
       <c r="J88" t="n">
-        <v>15.74</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="89">
@@ -3515,10 +3531,10 @@
         <v>88</v>
       </c>
       <c r="D89" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E89" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F89" t="n">
         <v>70</v>
@@ -3528,10 +3544,10 @@
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>0.154</v>
+        <v>0.158</v>
       </c>
       <c r="J89" t="n">
-        <v>13.25</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="90">
@@ -3549,10 +3565,10 @@
         <v>89</v>
       </c>
       <c r="D90" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E90" t="n">
-        <v>-86</v>
+        <v>-84</v>
       </c>
       <c r="F90" t="n">
         <v>164</v>
@@ -3562,150 +3578,146 @@
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>0.644</v>
+        <v>0.668</v>
       </c>
       <c r="J90" t="n">
-        <v>23.89</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>90</v>
       </c>
       <c r="D91" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="E91" t="n">
-        <v>12</v>
+        <v>-23</v>
       </c>
       <c r="F91" t="n">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G91" t="n">
-        <v>15.53</v>
+        <v>14.61</v>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>0.206</v>
+        <v>0.537</v>
       </c>
       <c r="J91" t="n">
-        <v>15.89</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>91</v>
       </c>
       <c r="D92" t="n">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="E92" t="n">
-        <v>-56</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G92" t="n">
-        <v>12.63</v>
+        <v>13.22</v>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
-        <v>0.642</v>
+        <v>0.309</v>
       </c>
       <c r="J92" t="n">
-        <v>31.26</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>RJ Harvey</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>92</v>
       </c>
       <c r="D93" t="n">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="E93" t="n">
-        <v>-41</v>
+        <v>19</v>
       </c>
       <c r="F93" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="G93" t="n">
-        <v>13.22</v>
+        <v>15.53</v>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>0.443</v>
+        <v>0.196</v>
       </c>
       <c r="J93" t="n">
-        <v>10.65</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>93</v>
       </c>
       <c r="D94" t="n">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="E94" t="n">
-        <v>-51</v>
+        <v>44</v>
       </c>
       <c r="F94" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="G94" t="n">
         <v>13.81</v>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>0.618</v>
+        <v>0.228</v>
       </c>
       <c r="J94" t="n">
-        <v>14.4</v>
+        <v>15.07</v>
       </c>
     </row>
     <row r="95">
@@ -3723,10 +3735,10 @@
         <v>94</v>
       </c>
       <c r="D95" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="E95" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="F95" t="n">
         <v>59</v>
@@ -3736,71 +3748,71 @@
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>0.296</v>
+        <v>0.294</v>
       </c>
       <c r="J95" t="n">
-        <v>13.64</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Travis Kelce</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>95</v>
       </c>
       <c r="D96" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E96" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F96" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="G96" t="n">
-        <v>13.81</v>
+        <v>16.37</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>0.196</v>
+        <v>0.177</v>
       </c>
       <c r="J96" t="n">
-        <v>14.76</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>96</v>
       </c>
       <c r="D97" t="n">
-        <v>127</v>
+        <v>200</v>
       </c>
       <c r="E97" t="n">
-        <v>-31</v>
+        <v>-104</v>
       </c>
       <c r="F97" t="n">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="G97" t="n">
-        <v>12.73</v>
+        <v>7.07</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3808,37 +3820,37 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.38</v>
+        <v>0.906</v>
       </c>
       <c r="J97" t="n">
-        <v>16.59</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>97</v>
       </c>
       <c r="D98" t="n">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="E98" t="n">
-        <v>-111</v>
+        <v>-32</v>
       </c>
       <c r="F98" t="n">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="G98" t="n">
-        <v>7.07</v>
+        <v>12.73</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3846,54 +3858,50 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.413</v>
       </c>
       <c r="J98" t="n">
-        <v>21.24</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>98</v>
       </c>
       <c r="D99" t="n">
-        <v>215</v>
+        <v>65</v>
       </c>
       <c r="E99" t="n">
-        <v>-117</v>
+        <v>33</v>
       </c>
       <c r="F99" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="G99" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>PUP</t>
-        </is>
-      </c>
+        <v>15.99</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.188</v>
       </c>
       <c r="J99" t="n">
-        <v>20.96</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3905,63 +3913,67 @@
         <v>99</v>
       </c>
       <c r="D100" t="n">
-        <v>68</v>
+        <v>174</v>
       </c>
       <c r="E100" t="n">
-        <v>31</v>
+        <v>-75</v>
       </c>
       <c r="F100" t="n">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="G100" t="n">
-        <v>15.99</v>
+        <v>12.53</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>0.167</v>
+        <v>0.637</v>
       </c>
       <c r="J100" t="n">
-        <v>13.65</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>100</v>
       </c>
       <c r="D101" t="n">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E101" t="n">
-        <v>-72</v>
+        <v>-58</v>
       </c>
       <c r="F101" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="G101" t="n">
-        <v>12.53</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
+        <v>12.44</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.604</v>
+        <v>0.714</v>
       </c>
       <c r="J101" t="n">
-        <v>15.34</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3973,67 +3985,67 @@
         <v>101</v>
       </c>
       <c r="D102" t="n">
-        <v>50</v>
+        <v>378</v>
       </c>
       <c r="E102" t="n">
-        <v>51</v>
+        <v>-277</v>
       </c>
       <c r="F102" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="G102" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="H102" t="inlineStr"/>
+        <v>10.31</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.195</v>
+        <v>0.84</v>
       </c>
       <c r="J102" t="n">
-        <v>9.59</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>102</v>
       </c>
       <c r="D103" t="n">
-        <v>359</v>
+        <v>68</v>
       </c>
       <c r="E103" t="n">
-        <v>-257</v>
+        <v>34</v>
       </c>
       <c r="F103" t="n">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G103" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>13.03</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="n">
-        <v>0.921</v>
+        <v>0.435</v>
       </c>
       <c r="J103" t="n">
-        <v>12.44</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Jakobi Meyers</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4045,27 +4057,23 @@
         <v>103</v>
       </c>
       <c r="D104" t="n">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E104" t="n">
-        <v>-57</v>
+        <v>-41</v>
       </c>
       <c r="F104" t="n">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="G104" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>12.63</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>0.716</v>
+        <v>0.648</v>
       </c>
       <c r="J104" t="n">
-        <v>17.95</v>
+        <v>34.81</v>
       </c>
     </row>
     <row r="105">
@@ -4083,10 +4091,10 @@
         <v>104</v>
       </c>
       <c r="D105" t="n">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E105" t="n">
-        <v>-20</v>
+        <v>30</v>
       </c>
       <c r="F105" t="n">
         <v>108</v>
@@ -4096,16 +4104,16 @@
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>0.388</v>
+        <v>0.24</v>
       </c>
       <c r="J105" t="n">
-        <v>13.13</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jakobi Meyers</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4117,23 +4125,27 @@
         <v>105</v>
       </c>
       <c r="D106" t="n">
-        <v>64</v>
+        <v>157</v>
       </c>
       <c r="E106" t="n">
-        <v>41</v>
+        <v>-52</v>
       </c>
       <c r="F106" t="n">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="G106" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="H106" t="inlineStr"/>
+        <v>14.44</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>0.414</v>
+        <v>0.707</v>
       </c>
       <c r="J106" t="n">
-        <v>14.38</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="107">
@@ -4164,10 +4176,10 @@
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
-        <v>0.514</v>
+        <v>0.516</v>
       </c>
       <c r="J107" t="n">
-        <v>17.5</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="108">
@@ -4185,10 +4197,10 @@
         <v>107</v>
       </c>
       <c r="D108" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E108" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F108" t="n">
         <v>94</v>
@@ -4198,150 +4210,150 @@
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
-        <v>0.213</v>
+        <v>0.2</v>
       </c>
       <c r="J108" t="n">
-        <v>9.59</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>108</v>
       </c>
       <c r="D109" t="n">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="E109" t="n">
-        <v>6</v>
+        <v>-29</v>
       </c>
       <c r="F109" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G109" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>14.79</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>0.276</v>
+        <v>0.65</v>
       </c>
       <c r="J109" t="n">
-        <v>15.18</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>109</v>
       </c>
       <c r="D110" t="n">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="E110" t="n">
-        <v>-27</v>
+        <v>28</v>
       </c>
       <c r="F110" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="G110" t="n">
-        <v>14.79</v>
+        <v>15.99</v>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>0.641</v>
+        <v>0.232</v>
       </c>
       <c r="J110" t="n">
-        <v>18.12</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Dalton Kincaid</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>110</v>
       </c>
       <c r="D111" t="n">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="E111" t="n">
-        <v>25</v>
+        <v>-24</v>
       </c>
       <c r="F111" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G111" t="n">
-        <v>15.99</v>
+        <v>13.29</v>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
-        <v>0.221</v>
+        <v>0.521</v>
       </c>
       <c r="J111" t="n">
-        <v>14.05</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Dalton Kincaid</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C112" t="n">
         <v>111</v>
       </c>
       <c r="D112" t="n">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="E112" t="n">
-        <v>-27</v>
+        <v>10</v>
       </c>
       <c r="F112" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="G112" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="H112" t="inlineStr"/>
+        <v>14.88</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>0.484</v>
+        <v>0.287</v>
       </c>
       <c r="J112" t="n">
-        <v>16.03</v>
+        <v>16.82</v>
       </c>
     </row>
     <row r="113">
@@ -4372,16 +4384,16 @@
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>0.661</v>
+        <v>0.632</v>
       </c>
       <c r="J113" t="n">
-        <v>11.35</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4393,29 +4405,33 @@
         <v>113</v>
       </c>
       <c r="D114" t="n">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="E114" t="n">
-        <v>-56</v>
+        <v>-29</v>
       </c>
       <c r="F114" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="G114" t="n">
-        <v>12.47</v>
-      </c>
-      <c r="H114" t="inlineStr"/>
+        <v>14.73</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>0.59</v>
+        <v>0.439</v>
       </c>
       <c r="J114" t="n">
-        <v>15.5</v>
+        <v>15.39</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4427,33 +4443,29 @@
         <v>114</v>
       </c>
       <c r="D115" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="E115" t="n">
-        <v>-66</v>
+        <v>-21</v>
       </c>
       <c r="F115" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="G115" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>14.1</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>0.66</v>
+        <v>0.413</v>
       </c>
       <c r="J115" t="n">
-        <v>15.21</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4465,135 +4477,135 @@
         <v>115</v>
       </c>
       <c r="D116" t="n">
+        <v>167</v>
+      </c>
+      <c r="E116" t="n">
+        <v>-52</v>
+      </c>
+      <c r="F116" t="n">
         <v>145</v>
       </c>
-      <c r="E116" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F116" t="n">
-        <v>135</v>
-      </c>
       <c r="G116" t="n">
-        <v>14.73</v>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>12.47</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>0.41</v>
+        <v>0.603</v>
       </c>
       <c r="J116" t="n">
-        <v>13.55</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Jake Ferguson</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>116</v>
       </c>
       <c r="D117" t="n">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="E117" t="n">
-        <v>33</v>
+        <v>-14</v>
       </c>
       <c r="F117" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="G117" t="n">
-        <v>15.17</v>
+        <v>14.79</v>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>0.281</v>
+        <v>0.61</v>
       </c>
       <c r="J117" t="n">
-        <v>19.08</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>117</v>
       </c>
       <c r="D118" t="n">
-        <v>58</v>
+        <v>178</v>
       </c>
       <c r="E118" t="n">
-        <v>59</v>
+        <v>-61</v>
       </c>
       <c r="F118" t="n">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="G118" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
+        <v>13.23</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.235</v>
+        <v>0.677</v>
       </c>
       <c r="J118" t="n">
-        <v>10.71</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>118</v>
       </c>
       <c r="D119" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="E119" t="n">
-        <v>-22</v>
+        <v>-37</v>
       </c>
       <c r="F119" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G119" t="n">
-        <v>14.1</v>
+        <v>12.81</v>
       </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>0.373</v>
+        <v>0.629</v>
       </c>
       <c r="J119" t="n">
-        <v>16.02</v>
+        <v>16.72</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Dallas Goedert</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4605,29 +4617,29 @@
         <v>119</v>
       </c>
       <c r="D120" t="n">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E120" t="n">
-        <v>-38</v>
+        <v>37</v>
       </c>
       <c r="F120" t="n">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="G120" t="n">
-        <v>12.81</v>
+        <v>15.17</v>
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>0.601</v>
+        <v>0.291</v>
       </c>
       <c r="J120" t="n">
-        <v>17.3</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Jordan Love</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4639,61 +4651,57 @@
         <v>120</v>
       </c>
       <c r="D121" t="n">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="E121" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="F121" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G121" t="n">
-        <v>15.11</v>
+        <v>16.37</v>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>0.332</v>
+        <v>0.172</v>
       </c>
       <c r="J121" t="n">
-        <v>10.1</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Khalil Shakir</t>
+          <t>Jordan Love</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>121</v>
       </c>
       <c r="D122" t="n">
-        <v>115</v>
+        <v>161</v>
       </c>
       <c r="E122" t="n">
-        <v>6</v>
+        <v>-40</v>
       </c>
       <c r="F122" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G122" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>15.11</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
-        <v>0.519</v>
+        <v>0.48</v>
       </c>
       <c r="J122" t="n">
-        <v>17.3</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="123">
@@ -4711,10 +4719,10 @@
         <v>122</v>
       </c>
       <c r="D123" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E123" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F123" t="n">
         <v>113</v>
@@ -4724,16 +4732,16 @@
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>0.337</v>
+        <v>0.347</v>
       </c>
       <c r="J123" t="n">
-        <v>25.82</v>
+        <v>29.71</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Khalil Shakir</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4745,23 +4753,27 @@
         <v>123</v>
       </c>
       <c r="D124" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="E124" t="n">
-        <v>-7</v>
+        <v>7</v>
       </c>
       <c r="F124" t="n">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="G124" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="H124" t="inlineStr"/>
+        <v>14.44</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>0.594</v>
+        <v>0.528</v>
       </c>
       <c r="J124" t="n">
-        <v>28.89</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="125">
@@ -4779,10 +4791,10 @@
         <v>124</v>
       </c>
       <c r="D125" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E125" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="F125" t="n">
         <v>66</v>
@@ -4792,10 +4804,10 @@
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
-        <v>0.607</v>
+        <v>0.613</v>
       </c>
       <c r="J125" t="n">
-        <v>17.23</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="126">
@@ -4813,10 +4825,10 @@
         <v>125</v>
       </c>
       <c r="D126" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E126" t="n">
-        <v>-37</v>
+        <v>-45</v>
       </c>
       <c r="F126" t="n">
         <v>105</v>
@@ -4826,16 +4838,16 @@
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
-        <v>0.55</v>
+        <v>0.534</v>
       </c>
       <c r="J126" t="n">
-        <v>16.15</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4847,27 +4859,23 @@
         <v>126</v>
       </c>
       <c r="D127" t="n">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="E127" t="n">
-        <v>-35</v>
+        <v>-12</v>
       </c>
       <c r="F127" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="G127" t="n">
-        <v>13.44</v>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>14.61</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
-        <v>0.732</v>
+        <v>0.604</v>
       </c>
       <c r="J127" t="n">
-        <v>15.16</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="128">
@@ -4885,10 +4893,10 @@
         <v>127</v>
       </c>
       <c r="D128" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E128" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F128" t="n">
         <v>114</v>
@@ -4898,184 +4906,184 @@
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="n">
-        <v>0.531</v>
+        <v>0.537</v>
       </c>
       <c r="J128" t="n">
-        <v>19.75</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>Malik Willis</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>128</v>
       </c>
       <c r="D129" t="n">
-        <v>141</v>
+        <v>336</v>
       </c>
       <c r="E129" t="n">
-        <v>-13</v>
+        <v>-208</v>
       </c>
       <c r="F129" t="n">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="G129" t="n">
-        <v>14.61</v>
+        <v>11.49</v>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>0.595</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>17.65</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mark Andrews</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>129</v>
       </c>
       <c r="D130" t="n">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="E130" t="n">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F130" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="G130" t="n">
-        <v>15.83</v>
+        <v>15.24</v>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
-        <v>0.21</v>
+        <v>0.537</v>
       </c>
       <c r="J130" t="n">
-        <v>25.49</v>
+        <v>16.31</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Malik Willis</t>
+          <t>Mark Andrews</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>130</v>
       </c>
       <c r="D131" t="n">
-        <v>229</v>
+        <v>62</v>
       </c>
       <c r="E131" t="n">
-        <v>-99</v>
+        <v>68</v>
       </c>
       <c r="F131" t="n">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G131" t="n">
-        <v>11.49</v>
+        <v>15.83</v>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
-        <v>0.759</v>
+        <v>0.237</v>
       </c>
       <c r="J131" t="n">
-        <v>25.82</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Juwan Johnson</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C132" t="n">
         <v>131</v>
       </c>
       <c r="D132" t="n">
-        <v>192</v>
+        <v>71</v>
       </c>
       <c r="E132" t="n">
-        <v>-61</v>
+        <v>60</v>
       </c>
       <c r="F132" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="G132" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Doubtful</t>
-        </is>
-      </c>
+        <v>16.12</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>0.883</v>
+        <v>0.256</v>
       </c>
       <c r="J132" t="n">
-        <v>28.65</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Juwan Johnson</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C133" t="n">
         <v>132</v>
       </c>
       <c r="D133" t="n">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="E133" t="n">
-        <v>62</v>
+        <v>-58</v>
       </c>
       <c r="F133" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="G133" t="n">
-        <v>16.12</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
+        <v>11.79</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Doubtful</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>0.21</v>
+        <v>0.862</v>
       </c>
       <c r="J133" t="n">
-        <v>22.17</v>
+        <v>29.74</v>
       </c>
     </row>
     <row r="134">
@@ -5093,10 +5101,10 @@
         <v>133</v>
       </c>
       <c r="D134" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E134" t="n">
-        <v>-38</v>
+        <v>-36</v>
       </c>
       <c r="F134" t="n">
         <v>165</v>
@@ -5106,10 +5114,10 @@
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
-        <v>0.588</v>
+        <v>0.598</v>
       </c>
       <c r="J134" t="n">
-        <v>14.91</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="135">
@@ -5140,146 +5148,150 @@
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="n">
-        <v>0.615</v>
+        <v>0.63</v>
       </c>
       <c r="J135" t="n">
-        <v>16.09</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Deebo Samuel</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C136" t="n">
         <v>135</v>
       </c>
       <c r="D136" t="n">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="E136" t="n">
-        <v>-16</v>
+        <v>-54</v>
       </c>
       <c r="F136" t="n">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="G136" t="n">
-        <v>14.96</v>
+        <v>15.99</v>
       </c>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="n">
-        <v>0.637</v>
+        <v>0.734</v>
       </c>
       <c r="J136" t="n">
-        <v>30.91</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C137" t="n">
         <v>136</v>
       </c>
       <c r="D137" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E137" t="n">
-        <v>-62</v>
+        <v>-61</v>
       </c>
       <c r="F137" t="n">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="G137" t="n">
-        <v>15.99</v>
-      </c>
-      <c r="H137" t="inlineStr"/>
+        <v>12.99</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>0.763</v>
+        <v>0.864</v>
       </c>
       <c r="J137" t="n">
-        <v>13.38</v>
+        <v>43.23</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Chris Rodriguez</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C138" t="n">
         <v>137</v>
       </c>
       <c r="D138" t="n">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="E138" t="n">
-        <v>55</v>
+        <v>-40</v>
       </c>
       <c r="F138" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="G138" t="n">
-        <v>16.37</v>
+        <v>12.21</v>
       </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="n">
-        <v>0.285</v>
+        <v>0.655</v>
       </c>
       <c r="J138" t="n">
-        <v>17.69</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Chris Rodriguez</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>138</v>
       </c>
       <c r="D139" t="n">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="E139" t="n">
-        <v>-39</v>
+        <v>68</v>
       </c>
       <c r="F139" t="n">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="G139" t="n">
-        <v>12.21</v>
+        <v>16.37</v>
       </c>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
-        <v>0.632</v>
+        <v>0.221</v>
       </c>
       <c r="J139" t="n">
-        <v>19.67</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="140">
@@ -5297,10 +5309,10 @@
         <v>139</v>
       </c>
       <c r="D140" t="n">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="E140" t="n">
-        <v>2</v>
+        <v>-48</v>
       </c>
       <c r="F140" t="n">
         <v>133</v>
@@ -5310,50 +5322,50 @@
       </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
-        <v>0.417</v>
+        <v>0.592</v>
       </c>
       <c r="J140" t="n">
-        <v>18.56</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C141" t="n">
         <v>140</v>
       </c>
       <c r="D141" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="E141" t="n">
-        <v>-23</v>
+        <v>-41</v>
       </c>
       <c r="F141" t="n">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="G141" t="n">
-        <v>14.61</v>
+        <v>12.91</v>
       </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
-        <v>0.534</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J141" t="n">
-        <v>14.25</v>
+        <v>24.58</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Deebo Samuel</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5365,67 +5377,63 @@
         <v>141</v>
       </c>
       <c r="D142" t="n">
-        <v>206</v>
+        <v>147</v>
       </c>
       <c r="E142" t="n">
-        <v>-65</v>
+        <v>-6</v>
       </c>
       <c r="F142" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="G142" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>14.96</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
-        <v>0.883</v>
+        <v>0.645</v>
       </c>
       <c r="J142" t="n">
-        <v>46.31</v>
+        <v>33.48</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Daniel Jones</t>
+          <t>Dylan Sampson</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C143" t="n">
         <v>142</v>
       </c>
       <c r="D143" t="n">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="E143" t="n">
-        <v>-45</v>
+        <v>-20</v>
       </c>
       <c r="F143" t="n">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="G143" t="n">
-        <v>12.91</v>
+        <v>14.61</v>
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>0.616</v>
+        <v>0.555</v>
       </c>
       <c r="J143" t="n">
-        <v>28.06</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Denzel Boston</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5437,29 +5445,29 @@
         <v>143</v>
       </c>
       <c r="D144" t="n">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="E144" t="n">
-        <v>-56</v>
+        <v>17</v>
       </c>
       <c r="F144" t="n">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="G144" t="n">
-        <v>14.79</v>
+        <v>13.03</v>
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
-        <v>0.872</v>
+        <v>0.534</v>
       </c>
       <c r="J144" t="n">
-        <v>34.66</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Tyrone Tracy</t>
+          <t>Keaton Mitchell</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5471,29 +5479,33 @@
         <v>144</v>
       </c>
       <c r="D145" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="E145" t="n">
-        <v>-59</v>
+        <v>-77</v>
       </c>
       <c r="F145" t="n">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G145" t="n">
-        <v>15.36</v>
-      </c>
-      <c r="H145" t="inlineStr"/>
+        <v>10.16</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Questionable</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>0.783</v>
+        <v>0.842</v>
       </c>
       <c r="J145" t="n">
-        <v>27.03</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5505,57 +5517,57 @@
         <v>145</v>
       </c>
       <c r="D146" t="n">
-        <v>128</v>
+        <v>194</v>
       </c>
       <c r="E146" t="n">
-        <v>17</v>
+        <v>-49</v>
       </c>
       <c r="F146" t="n">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G146" t="n">
-        <v>13.03</v>
+        <v>14.79</v>
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
-        <v>0.535</v>
+        <v>0.856</v>
       </c>
       <c r="J146" t="n">
-        <v>15.65</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Keaton Mitchell</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C147" t="n">
         <v>146</v>
       </c>
       <c r="D147" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E147" t="n">
-        <v>-68</v>
+        <v>-70</v>
       </c>
       <c r="F147" t="n">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="G147" t="n">
-        <v>10.96</v>
+        <v>16.08</v>
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
-        <v>0.806</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J147" t="n">
-        <v>28.77</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="148">
@@ -5573,10 +5585,10 @@
         <v>147</v>
       </c>
       <c r="D148" t="n">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="E148" t="n">
-        <v>-240</v>
+        <v>-224</v>
       </c>
       <c r="F148" t="n">
         <v>192</v>
@@ -5590,50 +5602,50 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="J148" t="n">
-        <v>29.63</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Jonah Coleman</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="C149" t="n">
         <v>148</v>
       </c>
       <c r="D149" t="n">
-        <v>165</v>
+        <v>258</v>
       </c>
       <c r="E149" t="n">
-        <v>-17</v>
+        <v>-110</v>
       </c>
       <c r="F149" t="n">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="G149" t="n">
-        <v>16.08</v>
+        <v>14.28</v>
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
-        <v>0.546</v>
+        <v>0.914</v>
       </c>
       <c r="J149" t="n">
-        <v>24.24</v>
+        <v>29.32</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Chig Okonkwo</t>
+          <t>Brenton Strange</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5645,61 +5657,57 @@
         <v>149</v>
       </c>
       <c r="D150" t="n">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="E150" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="F150" t="n">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="G150" t="n">
-        <v>16.12</v>
+        <v>14.54</v>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
-        <v>0.283</v>
+        <v>0.518</v>
       </c>
       <c r="J150" t="n">
-        <v>26.2</v>
+        <v>23.77</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Alvin Kamara</t>
+          <t>Chig Okonkwo</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>150</v>
       </c>
       <c r="D151" t="n">
-        <v>303</v>
+        <v>89</v>
       </c>
       <c r="E151" t="n">
-        <v>-153</v>
+        <v>61</v>
       </c>
       <c r="F151" t="n">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="G151" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Questionable</t>
-        </is>
-      </c>
+        <v>16.12</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>0.972</v>
+        <v>0.308</v>
       </c>
       <c r="J151" t="n">
-        <v>31.09</v>
+        <v>24.34</v>
       </c>
     </row>
   </sheetData>
